--- a/docs/StructureDefinition-MedRequestOrigXXXMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedRequestOrigXXXMedicationRequest.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-MedRequestOrigXXXMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedRequestOrigXXXMedicationRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case MedRequestOrigXXX, ResourceType MedicationRequest</t>
+    <t>This StructureDefinition contains the maps for VistA PRESCRIPTION (file 52) to FHIR MedicationRequest</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-MedRequestOrigXXXMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedRequestOrigXXXMedicationRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRequestOrigXXXMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedRequestOrigXXXMedicationRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRequestOrigXXXMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedRequestOrigXXXMedicationRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRequestOrigXXXMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedRequestOrigXXXMedicationRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRequestOrigXXXMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedRequestOrigXXXMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -252,10 +252,10 @@
     <t>Mapping: HL7 v2 Mapping</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t>Prescription
@@ -1795,10 +1795,10 @@
     <t>RXE-12-Number of Refills</t>
   </si>
   <si>
+    <t>816: source value from PRESCRIPTION - # OF REFILLS (#52-9)</t>
+  </si>
+  <si>
     <t>RxOut.RxOutpat.MaxRefills</t>
-  </si>
-  <si>
-    <t>816: source value from PRESCRIPTION - # OF REFILLS (#52-9)</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.quantity</t>
@@ -2346,8 +2346,8 @@
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="128.41796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="43.94140625" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="43.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11555,10 +11555,10 @@
         <v>559</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>83</v>
+        <v>560</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>560</v>
+        <v>83</v>
       </c>
     </row>
     <row r="76" hidden="true">

--- a/docs/StructureDefinition-MedRequestOrigXXXMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedRequestOrigXXXMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRequestOrigXXXMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedRequestOrigXXXMedicationRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRequestOrigXXXMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedRequestOrigXXXMedicationRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRequestOrigXXXMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedRequestOrigXXXMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRequestOrigXXXMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedRequestOrigXXXMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
